--- a/tables/PCA_var.xlsx
+++ b/tables/PCA_var.xlsx
@@ -77,7 +77,7 @@
     <t>See data sources of MGWR stage</t>
   </si>
   <si>
-    <t>motorable road nexwork</t>
+    <t>motorable road network</t>
   </si>
   <si>
     <t xml:space="preserve">Motorable Road: Length of major road network per km² </t>
@@ -86,7 +86,7 @@
     <t>Available from OSM road hierarchy (highway=*, e.g. trunk, primary)</t>
   </si>
   <si>
-    <t>OpenSteetMap (2025)</t>
+    <t>OpenStreetMap (2025)</t>
   </si>
   <si>
     <t>amenities poi</t>
